--- a/data/ovsg.xlsx
+++ b/data/ovsg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E445CA38-6961-3246-8E99-C21B5685155F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA77D783-8982-954D-91E9-B9B73B8EF4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="18" r:id="rId1"/>
     <sheet name="Doel" sheetId="6" r:id="rId2"/>
-    <sheet name="Leerplan" sheetId="17" r:id="rId3"/>
+    <sheet name="DoelCollectie" sheetId="17" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,12 +30,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>CODE</t>
-  </si>
-  <si>
-    <t>ingerichtDoor</t>
   </si>
   <si>
     <t>type</t>
@@ -610,15 +607,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -642,46 +639,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -697,8 +694,8 @@
   <cols>
     <col min="1" max="1" width="40" style="1" customWidth="1"/>
     <col min="2" max="2" width="60" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -706,167 +703,167 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">

--- a/data/ovsg.xlsx
+++ b/data/ovsg.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA77D783-8982-954D-91E9-B9B73B8EF4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4A85D0-C295-1548-BD85-F03401F698B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="18" r:id="rId1"/>
     <sheet name="Doel" sheetId="6" r:id="rId2"/>
     <sheet name="DoelCollectie" sheetId="17" r:id="rId3"/>
+    <sheet name="_customVoc" sheetId="19" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
   <si>
     <t>CODE</t>
   </si>
@@ -180,13 +181,43 @@
   </si>
   <si>
     <t>S-gr3</t>
+  </si>
+  <si>
+    <t>sheetLabel</t>
+  </si>
+  <si>
+    <t>sheetClass</t>
+  </si>
+  <si>
+    <t>columnLabel</t>
+  </si>
+  <si>
+    <t>columnProperty</t>
+  </si>
+  <si>
+    <t>valueDatatype</t>
+  </si>
+  <si>
+    <t>valueClass</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/Agent</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/title</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2001/XMLSchema#string</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +231,22 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -241,10 +288,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -257,8 +305,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -897,4 +948,63 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44523A96-3372-574B-88DA-C1CA5C6F0C01}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{3452C0AB-14EA-7A4D-B136-6C845E92A073}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{B35621E4-E5F4-E549-95E7-B1F14545C6D2}"/>
+    <hyperlink ref="E2" r:id="rId3" location="string" xr:uid="{D4E7B95B-AC6D-1843-B34E-DF9623D7E47E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>